--- a/naver-place-crawler/results_hair/송도_미용실.xlsx
+++ b/naver-place-crawler/results_hair/송도_미용실.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>플럭 송도 트리플타워 본점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>아치헤어 송도센트럴파크점</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>archihair@naver.com</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1410-0417</t>
+          <t>0507-1395-5750</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로28번길 8 트리플타워 EAST 상가 2층 223호</t>
+          <t>인천광역시 연수구 해돋이로171번길 11 201호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pluck_official/</t>
+          <t>https://blog.naver.com/archihair</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -597,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2912</v>
+        <v>2267</v>
       </c>
       <c r="Q2" t="n">
-        <v>106</v>
+        <v>658</v>
       </c>
       <c r="R2" t="n">
-        <v>3018</v>
+        <v>2925</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1167415255</t>
+          <t>1653822327</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1167415255</t>
+          <t>https://m.place.naver.com/place/1653822327</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -654,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>고정현헤어 쉐라톤점</t>
+          <t>라비앙르로즈 송도동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gohair7@naver.com</t>
+          <t>love77_jy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1411-3256</t>
+          <t>0507-1483-6616</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 153 쉐라톤호텔 6층</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 212호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.gohair.co.kr</t>
+          <t>https://www.instagram.com/lavieenrrose_songdo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -691,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1680</v>
+        <v>6577</v>
       </c>
       <c r="Q3" t="n">
-        <v>969</v>
+        <v>181</v>
       </c>
       <c r="R3" t="n">
-        <v>2649</v>
+        <v>6758</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13397872</t>
+          <t>1176079157</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13397872</t>
+          <t>https://m.place.naver.com/place/1176079157</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -748,29 +752,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아버헤어 트리플점</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>m_s_y_0219@naver.com</t>
-        </is>
-      </c>
+          <t>로맨시아 송도본점</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1407-9360</t>
+          <t>032-851-0606</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로16번길 33-1 트리플스트리트 A동 2층</t>
+          <t>인천광역시 연수구 랜드마크로 68 판매시설 301동 231호 로맨시아 송도본점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arborhair_official</t>
+          <t>http://www.instagram.com/romancia__salon</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>13141</v>
+        <v>3739</v>
       </c>
       <c r="Q4" t="n">
-        <v>1535</v>
+        <v>48</v>
       </c>
       <c r="R4" t="n">
-        <v>14676</v>
+        <v>3787</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>740312050</t>
+          <t>1759321108</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/740312050</t>
+          <t>https://m.place.naver.com/place/1759321108</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -842,25 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>노이브헤어</t>
+          <t>라벨르봄헤어살롱 송도본점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1348-5301</t>
+          <t>0507-1305-2402</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 301 2층 B동 2057호</t>
+          <t>인천광역시 연수구 인천타워대로 365 오피스텔 201동 2층 213호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noive.hair_official?igsh=MTR1aXZydjk3NnF5bg%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>514</v>
+        <v>759</v>
       </c>
       <c r="Q5" t="n">
-        <v>169</v>
+        <v>907</v>
       </c>
       <c r="R5" t="n">
-        <v>683</v>
+        <v>1666</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,51 +910,47 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2086898474</t>
+          <t>1328540463</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086898474</t>
+          <t>https://m.place.naver.com/place/1328540463</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>디폴트21 인천송도점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>yu-uy@naver.com</t>
-        </is>
-      </c>
+          <t>올룸</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1363-2273</t>
+          <t>0507-1304-7261</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-7 레드원프라자 107호</t>
+          <t>인천광역시 연수구 하모니로178번길 22 gtx센트럴 b동 304호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/default21.official/</t>
+          <t>https://www.instagram.com/allrum_seokheon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,13 +985,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1412</v>
+        <v>2080</v>
       </c>
       <c r="Q6" t="n">
-        <v>175</v>
+        <v>2464</v>
       </c>
       <c r="R6" t="n">
-        <v>1587</v>
+        <v>4544</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1000,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1941374338</t>
+          <t>1145024087</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941374338</t>
+          <t>https://m.place.naver.com/place/1145024087</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1026,25 +1022,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WE.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>오하루헤어 퍼스트파크점</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>o_haruhair@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1475-4245</t>
+          <t>0507-1314-5309</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 c동 409호</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 42 아라프라자 1층 125호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/we_0hun</t>
+          <t>https://blog.naver.com/o_haruhair</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1163</v>
+        <v>7045</v>
       </c>
       <c r="Q7" t="n">
-        <v>1594</v>
+        <v>2773</v>
       </c>
       <c r="R7" t="n">
-        <v>2757</v>
+        <v>9818</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1094,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1619386900</t>
+          <t>1708240266</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619386900</t>
+          <t>https://m.place.naver.com/place/1708240266</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1116,29 +1116,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>맨즈드옴므</t>
+          <t>아산테 송도점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mensdehomme@naver.com</t>
+          <t>jjae0410@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1481-5524</t>
+          <t>0507-1367-2313</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 아트포레 A동 312호 맨즈드옴므</t>
+          <t>인천광역시 연수구 하모니로 144 지웰푸르지오시티 A동 2층 210호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mensdehomme</t>
+          <t>https://www.instagram.com/asante_afro</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="Q8" t="n">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
-        <v>592</v>
+        <v>426</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,17 +1188,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1730928899</t>
+          <t>1985745417</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730928899</t>
+          <t>https://m.place.naver.com/place/1985745417</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라비앙르로즈 송도동점</t>
+          <t>WE.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1483-6616</t>
+          <t>0507-1475-4245</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 212호</t>
+          <t>인천광역시 연수구 하모니로 158 c동 409호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lavieenrrose_songdo</t>
+          <t>https://www.instagram.com/we_0hun</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>6551</v>
+        <v>1179</v>
       </c>
       <c r="Q9" t="n">
-        <v>184</v>
+        <v>1323</v>
       </c>
       <c r="R9" t="n">
-        <v>6735</v>
+        <v>2502</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1176079157</t>
+          <t>1619386900</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176079157</t>
+          <t>https://m.place.naver.com/place/1619386900</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1300,30 +1300,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리안헤어 송도랜시티점</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>니드어스헤어 인천송도점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>needus109@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1364-6808</t>
+          <t>0507-1487-7300</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 68 랜드마크시티센트럴더샵 1층(오피스텔 201동주차장검색)</t>
+          <t>인천광역시 연수구 신송로 157-15 제이큐브건물 2층 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/profile/c/riahn_landcity</t>
+          <t>https://www.instagram.com/needus_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1338,14 +1342,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3512</v>
+        <v>1268</v>
       </c>
       <c r="Q10" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="R10" t="n">
-        <v>3617</v>
+        <v>1427</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1372,17 +1372,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1118181179</t>
+          <t>2004520377</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118181179</t>
+          <t>https://m.place.naver.com/place/2004520377</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1394,29 +1394,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아인크헤어 인천송도점</t>
+          <t>에이바헤어 송도센트럴파크점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>aink_@naver.com</t>
+          <t>avaleedam@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1350-7471</t>
+          <t>0507-1475-1103</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 6 송도 중앙타워 2층 215, 216, 217호</t>
+          <t>인천광역시 연수구 해돋이로 168 혜인프라자 2층 203호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aink_</t>
+          <t>https://www.instagram.com/ava.leedam1103</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1442,7 +1442,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>9873</v>
+        <v>2259</v>
       </c>
       <c r="Q11" t="n">
-        <v>1842</v>
+        <v>1323</v>
       </c>
       <c r="R11" t="n">
-        <v>11715</v>
+        <v>3582</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1466,17 +1466,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1138093554</t>
+          <t>1944222724</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138093554</t>
+          <t>https://m.place.naver.com/place/1944222724</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스타일하우스 송도퍼스트파크점</t>
+          <t>리안헤어 송도아메리칸타운더샵점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>stylehousefp@naver.com</t>
+          <t>riahn0725@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1442-7926</t>
+          <t>0507-1395-5824</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A동 216호 스타일하우스 송도퍼스트파크점</t>
+          <t>인천광역시 연수구 송도과학로27번길 27 204-C동 2층 C217호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://youtube.com/@stylehouse_r</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>689</v>
+        <v>985</v>
       </c>
       <c r="Q12" t="n">
-        <v>1035</v>
+        <v>6356</v>
       </c>
       <c r="R12" t="n">
-        <v>1724</v>
+        <v>7341</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1560,17 +1560,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1895840787</t>
+          <t>2008265257</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895840787</t>
+          <t>https://m.place.naver.com/place/2008265257</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1582,25 +1582,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>오하루헤어 송도점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>스타일하우스 인천송도본점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>instylehouse@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1335-3086</t>
+          <t>0507-1430-7726</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 20 호반써밋 판매시설 110동 213호, 214호</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 송도밀레니엄 212호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.haruhair_official?igsh=cjAzeGRkZnBicmk5&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/instylehouse</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1615,7 +1619,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1635,13 +1639,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3895</v>
+        <v>3809</v>
       </c>
       <c r="Q13" t="n">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="R13" t="n">
-        <v>4130</v>
+        <v>4101</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1650,17 +1654,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1228447374</t>
+          <t>966103685</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228447374</t>
+          <t>https://m.place.naver.com/place/966103685</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1672,29 +1676,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26도헤어 송도점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>starch16@naver.com</t>
-        </is>
-      </c>
+          <t>비프론트 헤어살롱 송도점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1392-2625</t>
+          <t>032-433-4222</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 121 센타프라자 3층</t>
+          <t>인천광역시 연수구 아트센터대로 87 커넬워크 겨울동 402동 222~224호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/starch16</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5648</v>
+        <v>2280</v>
       </c>
       <c r="Q14" t="n">
-        <v>1679</v>
+        <v>451</v>
       </c>
       <c r="R14" t="n">
-        <v>7327</v>
+        <v>2731</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1353062492</t>
+          <t>13567369</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1353062492</t>
+          <t>https://m.place.naver.com/place/13567369</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1766,29 +1766,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>살롱루아</t>
+          <t>헤어마지 송도점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dlgmqlhd98@naver.com</t>
+          <t>joy79-@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1349-7525</t>
+          <t>0507-1440-1151</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 160 후문상가 1층 212동 102호 살롱루아</t>
+          <t>인천광역시 연수구 송도미래로11번길 27 A동 2층 A205호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/salon.lua</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1377</v>
+        <v>1489</v>
       </c>
       <c r="Q15" t="n">
-        <v>4076</v>
+        <v>174</v>
       </c>
       <c r="R15" t="n">
-        <v>5453</v>
+        <v>1663</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1838,17 +1838,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1156780755</t>
+          <t>1982871244</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156780755</t>
+          <t>https://m.place.naver.com/place/1982871244</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1860,20 +1860,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>비프론트 헤어살롱 송도점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>리안헤어 송도웨스턴파크점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>mindbookcoaching@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-433-4222</t>
+          <t>0507-1431-1006</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 87 커넬워크 겨울동 402동 222~224호</t>
+          <t>인천광역시 연수구 아트센터대로168번길 100 한라웨스턴파크송도 H동 1층 187호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1913,13 +1917,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2272</v>
+        <v>2078</v>
       </c>
       <c r="Q16" t="n">
-        <v>451</v>
+        <v>26</v>
       </c>
       <c r="R16" t="n">
-        <v>2723</v>
+        <v>2104</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1928,17 +1932,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13567369</t>
+          <t>1607090911</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13567369</t>
+          <t>https://m.place.naver.com/place/1607090911</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1950,29 +1954,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>무울헤어스튜디오</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>tldms105@naver.com</t>
-        </is>
-      </c>
+          <t>일랑헤어 송도센트럴점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1328-7105</t>
+          <t>0507-1375-9480</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 42 송도아라플라자 상가 117호</t>
+          <t>인천광역시 연수구 센트럴로 194 더샵센트럴파크2 A동 A2게이트 2층 216호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tldms105</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3097</v>
+        <v>318</v>
       </c>
       <c r="Q17" t="n">
-        <v>235</v>
+        <v>172</v>
       </c>
       <c r="R17" t="n">
-        <v>3332</v>
+        <v>490</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2022,17 +2022,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1625864632</t>
+          <t>2006323998</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1625864632</t>
+          <t>https://m.place.naver.com/place/2006323998</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2044,29 +2044,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>하리헤어</t>
+          <t>토리헤어 송도신도시점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rotjdakswjag@naver.com</t>
+          <t>nl7070@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1424-4505</t>
+          <t>0507-1382-3911</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 365 A동상가 3층</t>
+          <t>인천광역시 연수구 신송로 122 송도프라자 3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rotjdakswjag</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2101,13 +2101,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>202</v>
+        <v>2516</v>
       </c>
       <c r="Q18" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="R18" t="n">
-        <v>249</v>
+        <v>2541</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1355773815</t>
+          <t>1189703707</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1355773815</t>
+          <t>https://m.place.naver.com/place/1189703707</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2138,29 +2138,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>플럭 송도 타임스페이스점</t>
+          <t>송유헤어</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>iwonnie_you@naver.com</t>
+          <t>xyuni628@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1321-1538</t>
+          <t>0507-1396-3022</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 2층 C-202호</t>
+          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 325호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iwonnie_you</t>
+          <t>https://www.instagram.com/song.uhair</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>343</v>
+        <v>1625</v>
       </c>
       <c r="Q19" t="n">
-        <v>46</v>
+        <v>419</v>
       </c>
       <c r="R19" t="n">
-        <v>389</v>
+        <v>2044</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2210,42 +2210,42 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1607792315</t>
+          <t>1769465054</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1607792315</t>
+          <t>https://m.place.naver.com/place/1769465054</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>박승철 헤어스투디오 캠퍼스타운역점</t>
+          <t>제이디로얄 맨즈헤어 송도점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1404-9592</t>
+          <t>0507-1479-9326</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 27 204-C동 2층 C241호</t>
+          <t>인천광역시 연수구 연구단지로55번길 16 2층 235호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1069</v>
+        <v>983</v>
       </c>
       <c r="Q20" t="n">
-        <v>1035</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>2104</v>
+        <v>997</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2300,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2025219384</t>
+          <t>2091533314</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2025219384</t>
+          <t>https://m.place.naver.com/place/2091533314</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2322,29 +2322,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>리안헤어 송도하버뷰점</t>
+          <t>살롱디 송도본점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>musecafeco@naver.com</t>
+          <t>hairbygun@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1370-6181</t>
+          <t>0507-1411-8188</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 2층 201호</t>
+          <t>인천광역시 연수구 인천타워대로132번길 24 송도모아프라자 203호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/riahn_harborview/?igshid=ZmVmZTY5ZGE%3D</t>
+          <t>https://www.instagram.com/salond.203/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>4634</v>
+        <v>4477</v>
       </c>
       <c r="Q21" t="n">
-        <v>155</v>
+        <v>420</v>
       </c>
       <c r="R21" t="n">
-        <v>4789</v>
+        <v>4897</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2394,17 +2394,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1923217214</t>
+          <t>31274453</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1923217214</t>
+          <t>https://m.place.naver.com/place/31274453</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2416,29 +2416,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>제이디로얄 맨즈헤어 송도점</t>
+          <t>로커스 헤어</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sub_blog@naver.com</t>
+          <t>locus_hair@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1479-9326</t>
+          <t>0507-1362-9519</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 연구단지로55번길 16 2층 235호</t>
+          <t>인천광역시 연수구 송도과학로27번길 55 롯데캐슬 캠퍼스타운 A동 201호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/locus_hair</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>903</v>
+        <v>783</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R22" t="n">
-        <v>921</v>
+        <v>794</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2488,47 +2488,51 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2091533314</t>
+          <t>350879615</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2091533314</t>
+          <t>https://m.place.naver.com/place/350879615</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>매드맨즈헤어</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>26도헤어 송도점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>starch16@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1316-7719</t>
+          <t>0507-1392-2625</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 204호</t>
+          <t>인천광역시 연수구 신송로 121 센타프라자 3층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/starch16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2538,12 +2542,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2559,17 +2563,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1594</v>
+        <v>5664</v>
       </c>
       <c r="Q23" t="n">
-        <v>1692</v>
+        <v>1733</v>
       </c>
       <c r="R23" t="n">
-        <v>3286</v>
+        <v>7397</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2578,17 +2582,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1852738585</t>
+          <t>1353062492</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1852738585</t>
+          <t>https://m.place.naver.com/place/1353062492</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2600,25 +2604,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>쿨헤어</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>오하루헤어 송도점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>blablakimm@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1324-9494</t>
+          <t>0507-1335-3086</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-7 레드원프라자 3층</t>
+          <t>인천광역시 연수구 랜드마크로 20 호반써밋 판매시설 110동 213호, 214호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coolhair_songdo</t>
+          <t>https://www.instagram.com/o.haruhair_official?igsh=cjAzeGRkZnBicmk5&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2653,13 +2661,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2190</v>
+        <v>3957</v>
       </c>
       <c r="Q24" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="R24" t="n">
-        <v>2419</v>
+        <v>4192</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2668,51 +2676,51 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>703815652</t>
+          <t>1228447374</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/703815652</t>
+          <t>https://m.place.naver.com/place/1228447374</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>차홍룸 송도점</t>
+          <t>디폴트21 인천송도점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>chahong1@naver.com</t>
+          <t>yu-uy@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>032-831-3656</t>
+          <t>0507-1363-2273</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 워터프런트로 150 상가 A동 101동 311호</t>
+          <t>인천광역시 연수구 해돋이로 168-7 레드원프라자 107호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chahong1</t>
+          <t>https://www.instagram.com/default21.official/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2727,7 +2735,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2747,13 +2755,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3446</v>
+        <v>1416</v>
       </c>
       <c r="Q25" t="n">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="R25" t="n">
-        <v>3592</v>
+        <v>1590</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2762,17 +2770,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2044983354</t>
+          <t>1941374338</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044983354</t>
+          <t>https://m.place.naver.com/place/1941374338</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2784,29 +2792,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에이앤느 송도 타임스페이스 본점</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>aannehair@naver.com</t>
-        </is>
-      </c>
+          <t>박승철헤어스투디오 송도국제도시점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1445-0710</t>
+          <t>032-851-2326</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 303, 304호</t>
+          <t>인천광역시 연수구 신송로 121 센터프라자 2층 202호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://youtube.com/@aannetv</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2816,7 +2820,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2837,17 +2841,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3699</v>
+        <v>3971</v>
       </c>
       <c r="Q26" t="n">
-        <v>1396</v>
+        <v>237</v>
       </c>
       <c r="R26" t="n">
-        <v>5095</v>
+        <v>4208</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2856,51 +2860,47 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1640981582</t>
+          <t>13395671</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1640981582</t>
+          <t>https://m.place.naver.com/place/13395671</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>리안헤어 송도센트럴파크점</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>rlacksgh55@naver.com</t>
-        </is>
-      </c>
+          <t>어드맨즈 송도센트럴점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1333-9318</t>
+          <t>032-212-6149</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로171번길 11 리버리치아케이드 상가 2층 103동 225호 1호~호</t>
+          <t>인천광역시 연수구 센트럴로 232 E동 1층 179, 180호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/riahn_centralpark/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2931,17 +2931,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2456</v>
+        <v>196</v>
       </c>
       <c r="Q27" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2670</v>
+        <v>196</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2950,17 +2950,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1243347859</t>
+          <t>2084340217</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1243347859</t>
+          <t>https://m.place.naver.com/place/2084340217</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2972,29 +2972,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>일랑헤어 송도센트럴점</t>
+          <t>아인크헤어 인천송도점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wngud4638@naver.com</t>
+          <t>aink_@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1375-9480</t>
+          <t>0507-1350-7471</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 194 더샵센트럴파크2 A동 A2게이트 2층 216호</t>
+          <t>인천광역시 연수구 하모니로178번길 6 송도 중앙타워 2층 215, 216, 217호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/aink_</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>303</v>
+        <v>9929</v>
       </c>
       <c r="Q28" t="n">
-        <v>133</v>
+        <v>1862</v>
       </c>
       <c r="R28" t="n">
-        <v>436</v>
+        <v>11791</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3044,17 +3044,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2006323998</t>
+          <t>1138093554</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006323998</t>
+          <t>https://m.place.naver.com/place/1138093554</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3066,29 +3066,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>덕무드헤어 송도타임스페이스점</t>
+          <t>아티자</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>wooduk89@naver.com</t>
+          <t>artisign@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1449-0237</t>
+          <t>0507-1458-0182</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 B동 314호</t>
+          <t>인천광역시 연수구 인천타워대로180번길 11 A동 2층 212, 213호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wooduk89</t>
+          <t>https://www.instagram.com/atiza__official</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3123,13 +3123,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1225</v>
+        <v>529</v>
       </c>
       <c r="Q29" t="n">
-        <v>431</v>
+        <v>253</v>
       </c>
       <c r="R29" t="n">
-        <v>1656</v>
+        <v>782</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1163645359</t>
+          <t>1532848362</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163645359</t>
+          <t>https://m.place.naver.com/place/1532848362</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3160,29 +3160,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>아티자</t>
+          <t>오하루헤어 레이크점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>artisign@naver.com</t>
+          <t>o_haruhair@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1458-0182</t>
+          <t>0507-1420-3443</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로180번길 11 A동 2층 212, 213호</t>
+          <t>인천광역시 연수구 아카데미로312번길 31 439동 1층 105, 106호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/atiza__official</t>
+          <t>https://blog.naver.com/o_haruhair</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3213,17 +3213,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>513</v>
+        <v>1054</v>
       </c>
       <c r="Q30" t="n">
-        <v>247</v>
+        <v>127</v>
       </c>
       <c r="R30" t="n">
-        <v>760</v>
+        <v>1181</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3232,17 +3232,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1532848362</t>
+          <t>2044040468</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1532848362</t>
+          <t>https://m.place.naver.com/place/2044040468</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3254,29 +3254,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>살롱드포레라 송도점</t>
+          <t>고정현헤어 송도센트럴점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>forera_@naver.com</t>
+          <t>gohair7@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1491-2268</t>
+          <t>0507-1414-3256</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-15 글로벌시티프라자 201호</t>
+          <t>인천광역시 연수구 해돋이로 168-2 에스원타워 2층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/foreraconnect</t>
+          <t>http://www.gohair.co.kr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3311,13 +3311,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1928</v>
+        <v>5026</v>
       </c>
       <c r="Q31" t="n">
-        <v>84</v>
+        <v>1794</v>
       </c>
       <c r="R31" t="n">
-        <v>2012</v>
+        <v>6820</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3326,17 +3326,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1093275292</t>
+          <t>1992695361</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1093275292</t>
+          <t>https://m.place.naver.com/place/1992695361</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3348,29 +3348,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>에이바헤어 송도센트럴파크점</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>avaleedam@naver.com</t>
-        </is>
-      </c>
+          <t>리안헤어 송도웰카운티점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1475-1103</t>
+          <t>0507-1484-8214</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168 혜인프라자 2층 203호</t>
+          <t>인천광역시 연수구 인천타워대로54번길 9 에몬스프라자 1층 114호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ava.leedam1103</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3396,22 +3392,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2247</v>
+        <v>4672</v>
       </c>
       <c r="Q32" t="n">
-        <v>1358</v>
+        <v>11311</v>
       </c>
       <c r="R32" t="n">
-        <v>3605</v>
+        <v>15983</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3420,17 +3416,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1944222724</t>
+          <t>1649604041</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944222724</t>
+          <t>https://m.place.naver.com/place/1649604041</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3442,29 +3438,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>옵트헤어 인천송도점</t>
+          <t>고정현헤어 송도오네스타점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>cyclopedi35518@naver.com</t>
+          <t>gohair7@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1385-7108</t>
+          <t>0507-1304-3256</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 303호</t>
+          <t>인천광역시 연수구 송도국제대로 157 오네스타 지하 1층에 위치해 있습니다</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/obt_hair/?hl=ko</t>
+          <t>http://www.gohair.co.kr</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3479,7 +3475,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3499,13 +3495,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3508</v>
+        <v>8520</v>
       </c>
       <c r="Q33" t="n">
-        <v>1983</v>
+        <v>1131</v>
       </c>
       <c r="R33" t="n">
-        <v>5491</v>
+        <v>9651</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3514,17 +3510,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1473993571</t>
+          <t>1691517290</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1473993571</t>
+          <t>https://m.place.naver.com/place/1691517290</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3537,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sonmom_@naver.com</t>
+          <t>dyry1314@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3593,13 +3589,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1904</v>
+        <v>1958</v>
       </c>
       <c r="Q34" t="n">
-        <v>1420</v>
+        <v>1859</v>
       </c>
       <c r="R34" t="n">
-        <v>3324</v>
+        <v>3817</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3618,7 +3614,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3630,29 +3626,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>포레브헤어</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>loveru90@naver.com</t>
-        </is>
-      </c>
+          <t>로이드밤 송도점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1487-8813</t>
+          <t>032-833-6212</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 6 3층 312호</t>
+          <t>인천광역시 연수구 신송로125번길 13 아크리아1 2층 로이드밤</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/foreve_official</t>
+          <t>https://www.instagram.com/lloydbomb_songdo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3687,13 +3679,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2029</v>
+        <v>4093</v>
       </c>
       <c r="Q35" t="n">
-        <v>612</v>
+        <v>308</v>
       </c>
       <c r="R35" t="n">
-        <v>2641</v>
+        <v>4401</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3702,17 +3694,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1653032976</t>
+          <t>37547131</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653032976</t>
+          <t>https://m.place.naver.com/place/37547131</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3724,29 +3716,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도송</t>
+          <t>잇키</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>syht7712@naver.com</t>
+          <t>chl1192@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1465-7878</t>
+          <t>0507-1416-1192</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 313 씨워크인테라스한라 B동 2층 242호</t>
+          <t>인천광역시 연수구 인천타워대로180번길 11 B동 201, 202호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/syht7712</t>
+          <t>https://youtube.com/@itki_dooh</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3761,7 +3753,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3781,13 +3773,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>471</v>
+        <v>4885</v>
       </c>
       <c r="Q36" t="n">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="R36" t="n">
-        <v>548</v>
+        <v>5205</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3796,51 +3788,51 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1123348836</t>
+          <t>1455037434</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1123348836</t>
+          <t>https://m.place.naver.com/place/1455037434</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>살롱드세렌디 인천송도점</t>
+          <t>엑스디맨즈헤어</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>salon_serendi_@naver.com</t>
+          <t>xdmanshair@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1346-5035</t>
+          <t>0507-1345-1126</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로28번길 8 더샵 트리플타워 east동 208호 살롱 드 세렌디</t>
+          <t>인천광역시 연수구 인천타워대로180번길 11 더샵송도센트럴파크3차 상가A동 314호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salon_serendi</t>
+          <t>https://blog.naver.com/xdmanshair</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3855,7 +3847,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3875,13 +3867,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1972</v>
+        <v>758</v>
       </c>
       <c r="Q37" t="n">
-        <v>149</v>
+        <v>408</v>
       </c>
       <c r="R37" t="n">
-        <v>2121</v>
+        <v>1166</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3890,17 +3882,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1732434675</t>
+          <t>1677938717</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732434675</t>
+          <t>https://m.place.naver.com/place/1677938717</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3912,29 +3904,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>스타일하우스 인천송도본점</t>
+          <t>리안헤어 송도하버뷰점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>instylehouse@naver.com</t>
+          <t>musecafeco@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1430-7726</t>
+          <t>0507-1370-6181</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 69 송도밀레니엄 212호</t>
+          <t>인천광역시 연수구 해돋이로 160-19 카리스프라자 2층 201호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/instylehouse</t>
+          <t>https://www.instagram.com/riahn_harborview/?igshid=ZmVmZTY5ZGE%3D</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3949,7 +3941,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3969,13 +3961,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3785</v>
+        <v>4692</v>
       </c>
       <c r="Q38" t="n">
-        <v>284</v>
+        <v>154</v>
       </c>
       <c r="R38" t="n">
-        <v>4069</v>
+        <v>4846</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3984,17 +3976,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>966103685</t>
+          <t>1923217214</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/966103685</t>
+          <t>https://m.place.naver.com/place/1923217214</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4006,29 +3998,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이콘헤어살롱 송도트리플타워점</t>
+          <t>리안헤어 송도센트럴파크점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>iconkwon@naver.com</t>
+          <t>rlacksgh55@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1402-2998</t>
+          <t>0507-1333-9318</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로28번길 50 트리플타워west 2층 208호 아이콘헤어살롱</t>
+          <t>인천광역시 연수구 해돋이로171번길 11 리버리치아케이드 상가 2층 103동 225호 1호~호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/iconkwon</t>
+          <t>https://www.instagram.com/riahn_centralpark/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4043,7 +4035,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4059,17 +4051,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2880</v>
+        <v>2479</v>
       </c>
       <c r="Q39" t="n">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="R39" t="n">
-        <v>3021</v>
+        <v>2693</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4078,17 +4070,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>37927793</t>
+          <t>1243347859</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37927793</t>
+          <t>https://m.place.naver.com/place/1243347859</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4100,25 +4092,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>준오헤어 송도센트럴파크점</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>쿨헤어</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>oko2227@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1372-6605</t>
+          <t>0507-1324-9494</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 194 a동 2층 221호</t>
+          <t>인천광역시 연수구 해돋이로 168-7 레드원프라자 3층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/juno.hairsalon?igsh=cTI0NTZycDM4NWM%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/coolhair_songdo</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4153,13 +4149,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>18689</v>
+        <v>2204</v>
       </c>
       <c r="Q40" t="n">
-        <v>1000</v>
+        <v>232</v>
       </c>
       <c r="R40" t="n">
-        <v>19689</v>
+        <v>2436</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,17 +4164,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1341167720</t>
+          <t>703815652</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1341167720</t>
+          <t>https://m.place.naver.com/place/703815652</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4190,29 +4186,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>담다헤어살롱</t>
+          <t>살롱드포레라 송도점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>honii517@naver.com</t>
+          <t>forera_@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1329-8982</t>
+          <t>0507-1491-2268</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로168번길 100 F동 2층</t>
+          <t>인천광역시 연수구 해돋이로 168-15 글로벌시티프라자 201호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/damda_sooni</t>
+          <t>https://www.instagram.com/foreraconnect</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,13 +4243,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1622</v>
+        <v>1933</v>
       </c>
       <c r="Q41" t="n">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="R41" t="n">
-        <v>1814</v>
+        <v>2017</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4262,17 +4258,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1694632496</t>
+          <t>1093275292</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1694632496</t>
+          <t>https://m.place.naver.com/place/1093275292</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4284,29 +4280,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>리안헤어 송도웰카운티점</t>
+          <t>오하루헤어 에스파이브시티점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>g14778@naver.com</t>
+          <t>o_haruhair@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1484-8214</t>
+          <t>0507-1391-5519</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로54번길 9 에몬스프라자 1층 114호</t>
+          <t>인천광역시 연수구 첨단대로 40 A동 2층 A204호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/o_haruhair</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4316,12 +4312,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4341,13 +4337,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4515</v>
+        <v>3119</v>
       </c>
       <c r="Q42" t="n">
-        <v>11066</v>
+        <v>1989</v>
       </c>
       <c r="R42" t="n">
-        <v>15581</v>
+        <v>5108</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4356,51 +4352,51 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1649604041</t>
+          <t>2064437850</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1649604041</t>
+          <t>https://m.place.naver.com/place/2064437850</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>샵온무드 송도점</t>
+          <t>맨즈드옴므</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jej0010@naver.com</t>
+          <t>mensdehomme@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1366-2853</t>
+          <t>0507-1481-5524</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 165-17 월드메르디앙송도 108호</t>
+          <t>인천광역시 연수구 인천타워대로 257 아트포레 A동 312호 맨즈드옴므</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shop._.onmood</t>
+          <t>https://blog.naver.com/mensdehomme</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4415,7 +4411,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4435,13 +4431,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>287</v>
+        <v>446</v>
       </c>
       <c r="Q43" t="n">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="R43" t="n">
-        <v>383</v>
+        <v>636</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4450,17 +4446,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1003183969</t>
+          <t>1730928899</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003183969</t>
+          <t>https://m.place.naver.com/place/1730928899</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4472,29 +4468,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>본비반트헤어 송도센트럴파크점</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>pleas12@naver.com</t>
-        </is>
-      </c>
+          <t>마끼에 타임스페이스점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1445-2352</t>
+          <t>0507-1411-5326</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 232 D동 202호</t>
+          <t>인천광역시 연수구 하모니로 158 C동 307호, 308호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pleas12</t>
+          <t>http://www.instagram.com/maquillee_songdo</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4509,7 +4501,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4525,17 +4517,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2659</v>
+        <v>6290</v>
       </c>
       <c r="Q44" t="n">
-        <v>170</v>
+        <v>818</v>
       </c>
       <c r="R44" t="n">
-        <v>2829</v>
+        <v>7108</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4544,17 +4536,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>35372752</t>
+          <t>37058951</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35372752</t>
+          <t>https://m.place.naver.com/place/37058951</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4566,29 +4558,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 송도국제도시점</t>
+          <t>플럭 송도 트리플타워 본점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>hairsongdo@naver.com</t>
+          <t>wkdb753@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-851-2326</t>
+          <t>0507-1410-0417</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 121 센터프라자 2층 202호</t>
+          <t>인천광역시 연수구 송도과학로28번길 8 트리플타워 EAST 상가 2층 223호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hairsongdo</t>
+          <t>https://www.instagram.com/pluck_official/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4603,7 +4595,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4619,17 +4611,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3959</v>
+        <v>2946</v>
       </c>
       <c r="Q45" t="n">
-        <v>282</v>
+        <v>106</v>
       </c>
       <c r="R45" t="n">
-        <v>4241</v>
+        <v>3052</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4638,17 +4630,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13395671</t>
+          <t>1167415255</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13395671</t>
+          <t>https://m.place.naver.com/place/1167415255</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4660,29 +4652,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>아버헤어 트리플 2호점</t>
+          <t>살롱루아</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mindes0418@naver.com</t>
+          <t>dlgmqlhd98@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1332-9360</t>
+          <t>0507-1349-7525</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로16번길 33-4 트리플스트리트 D동 지하 1층</t>
+          <t>인천광역시 연수구 랜드마크로 160 후문상가 1층 212동 102호 살롱루아</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/salon.lua</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4692,7 +4684,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4713,17 +4705,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5731</v>
+        <v>1384</v>
       </c>
       <c r="Q46" t="n">
-        <v>850</v>
+        <v>4222</v>
       </c>
       <c r="R46" t="n">
-        <v>6581</v>
+        <v>5606</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4732,17 +4724,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1980016350</t>
+          <t>1156780755</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1980016350</t>
+          <t>https://m.place.naver.com/place/1156780755</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4754,20 +4746,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>리안헤어 송도아메리칸타운더샵점</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>아버헤어 트리플 2호점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mindes0418@naver.com</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1395-5824</t>
+          <t>0507-1332-9360</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 27 204-C동 2층 C217호</t>
+          <t>인천광역시 연수구 송도과학로16번길 33-4 트리플스트리트 D동 지하 1층</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4807,13 +4803,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>871</v>
+        <v>5801</v>
       </c>
       <c r="Q47" t="n">
-        <v>6170</v>
+        <v>818</v>
       </c>
       <c r="R47" t="n">
-        <v>7041</v>
+        <v>6619</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4822,17 +4818,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2008265257</t>
+          <t>1980016350</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2008265257</t>
+          <t>https://m.place.naver.com/place/1980016350</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4844,25 +4840,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>몰트베</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>헤이미살롱 송도점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>heyme1999@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1440-8389</t>
+          <t>032-833-1995</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 257 D동 2층 203호</t>
+          <t>인천광역시 연수구 신송로 161 하이츠 2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moltbe.hair</t>
+          <t>https://blog.naver.com/heyme1999</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4897,13 +4897,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>590</v>
+        <v>1183</v>
       </c>
       <c r="Q48" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="R48" t="n">
-        <v>659</v>
+        <v>1199</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4912,17 +4912,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1133641661</t>
+          <t>1566942448</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1133641661</t>
+          <t>https://m.place.naver.com/place/1566942448</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4934,29 +4934,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>잇키</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>chl1192@naver.com</t>
-        </is>
-      </c>
+          <t>옵트헤어 인천송도점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1416-1192</t>
+          <t>0507-1385-7108</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로180번길 11 B동 201, 202호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 303호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://youtube.com/@itki_dooh</t>
+          <t>https://www.instagram.com/obt_hair/?hl=ko</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4991,13 +4987,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>4745</v>
+        <v>3655</v>
       </c>
       <c r="Q49" t="n">
-        <v>243</v>
+        <v>2127</v>
       </c>
       <c r="R49" t="n">
-        <v>4988</v>
+        <v>5782</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5006,17 +5002,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1455037434</t>
+          <t>1473993571</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1455037434</t>
+          <t>https://m.place.naver.com/place/1473993571</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5028,34 +5024,30 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>살롱디 송도본점</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>hairbygun@naver.com</t>
-        </is>
-      </c>
+          <t>준오헤어 송도홈플러스점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1411-8188</t>
+          <t>0507-1398-0605</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로132번길 24 송도모아프라자 203호</t>
+          <t>인천광역시 연수구 송도국제대로 165 홈플러스2층 준오헤어송도홈플러스점</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/salond.203/</t>
+          <t>http://junohair.com/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5085,13 +5077,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4477</v>
+        <v>5381</v>
       </c>
       <c r="Q50" t="n">
-        <v>402</v>
+        <v>305</v>
       </c>
       <c r="R50" t="n">
-        <v>4879</v>
+        <v>5686</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5100,17 +5092,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>31274453</t>
+          <t>37207297</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31274453</t>
+          <t>https://m.place.naver.com/place/37207297</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5122,34 +5114,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>준오헤어 송도크리스탈오션점</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>badasoop_rimi@naver.com</t>
-        </is>
-      </c>
+          <t>담다헤어살롱</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1478-0692</t>
+          <t>0507-1329-8982</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로360번길 40 306동 101, 102호</t>
+          <t>인천광역시 연수구 아트센터대로168번길 100 F동 2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://junohair.com/</t>
+          <t>http://www.instagram.com/damda_sooni</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5179,13 +5167,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2045</v>
+        <v>1629</v>
       </c>
       <c r="Q51" t="n">
-        <v>49</v>
+        <v>190</v>
       </c>
       <c r="R51" t="n">
-        <v>2094</v>
+        <v>1819</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5194,17 +5182,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1895978509</t>
+          <t>1694632496</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895978509</t>
+          <t>https://m.place.naver.com/place/1694632496</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5216,29 +5204,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>송유헤어</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>shungyeon627@naver.com</t>
-        </is>
-      </c>
+          <t>아버헤어 트리플점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1396-3022</t>
+          <t>0507-1407-9360</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로138번길 11 송도캐슬센트럴파크 102동 325호</t>
+          <t>인천광역시 연수구 송도과학로16번길 33-1 트리플스트리트 A동 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/song.uhair</t>
+          <t>https://www.instagram.com/arborhair_official</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5273,13 +5257,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1600</v>
+        <v>13205</v>
       </c>
       <c r="Q52" t="n">
-        <v>408</v>
+        <v>1504</v>
       </c>
       <c r="R52" t="n">
-        <v>2008</v>
+        <v>14709</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5288,51 +5272,51 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1769465054</t>
+          <t>740312050</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1769465054</t>
+          <t>https://m.place.naver.com/place/740312050</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>남성전문미용실</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>아산테 송도점</t>
+          <t>하리헤어</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sinzzang70000@naver.com</t>
+          <t>rotjdakswjag@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1367-2313</t>
+          <t>0507-1424-4505</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 144 지웰푸르지오시티 A동 2층 210호</t>
+          <t>인천광역시 연수구 인천타워대로 365 A동상가 3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/asante_afro</t>
+          <t>https://blog.naver.com/rotjdakswjag</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5347,7 +5331,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5363,17 +5347,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>401</v>
+        <v>213</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
-        <v>424</v>
+        <v>259</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5382,17 +5366,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1985745417</t>
+          <t>1355773815</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1985745417</t>
+          <t>https://m.place.naver.com/place/1355773815</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5404,29 +5388,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>올룸</t>
+          <t>차홍룸 송도점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ddyohome@naver.com</t>
+          <t>chahong1@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1304-7261</t>
+          <t>032-831-3656</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로178번길 22 gtx센트럴 b동 304호</t>
+          <t>인천광역시 연수구 워터프런트로 150 상가 A동 101동 311호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allrum_seokheon</t>
+          <t>https://blog.naver.com/chahong1</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5441,7 +5425,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5461,13 +5445,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2020</v>
+        <v>3624</v>
       </c>
       <c r="Q54" t="n">
-        <v>2357</v>
+        <v>157</v>
       </c>
       <c r="R54" t="n">
-        <v>4377</v>
+        <v>3781</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5476,17 +5460,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1145024087</t>
+          <t>2044983354</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145024087</t>
+          <t>https://m.place.naver.com/place/2044983354</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5498,29 +5482,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>고정현헤어 송도센트럴점</t>
+          <t>소유헤어</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gohair7@naver.com</t>
+          <t>dmsrud_0724@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1414-3256</t>
+          <t>0507-1433-1221</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로 168-2 에스원타워 2층</t>
+          <t>인천광역시 연수구 센트럴로 232 센트럴1차상가 E동 150호 소유헤어</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://www.gohair.co.kr</t>
+          <t>https://blog.naver.com/dmsrud_0724</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5551,17 +5535,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>4995</v>
+        <v>1817</v>
       </c>
       <c r="Q55" t="n">
-        <v>1750</v>
+        <v>2360</v>
       </c>
       <c r="R55" t="n">
-        <v>6745</v>
+        <v>4177</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5570,17 +5554,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1992695361</t>
+          <t>1483623620</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992695361</t>
+          <t>https://m.place.naver.com/place/1483623620</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5592,29 +5576,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>오하루헤어 에스파이브시티점</t>
+          <t>아이디헤어 송도센트럴파크점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>o_haruhair@naver.com</t>
+          <t>rnalghoi@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1391-5519</t>
+          <t>0507-1490-1682</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 첨단대로 40 A동 2층 A204호</t>
+          <t>인천광역시 연수구 센트럴로 160 판매시설 C동 2층 아이디헤어</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/o_haruhair</t>
+          <t>https://blog.naver.com/rnalghoi?tab=1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5649,13 +5633,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3023</v>
+        <v>1428</v>
       </c>
       <c r="Q56" t="n">
-        <v>2001</v>
+        <v>1751</v>
       </c>
       <c r="R56" t="n">
-        <v>5024</v>
+        <v>3179</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5664,17 +5648,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2064437850</t>
+          <t>2010746176</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064437850</t>
+          <t>https://m.place.naver.com/place/2010746176</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5686,29 +5670,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>오하루헤어 퍼스트파크점</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>o_haruhair@naver.com</t>
-        </is>
-      </c>
+          <t>준오헤어 송도센트럴파크점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1314-5309</t>
+          <t>0507-1372-6605</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로230번길 42 아라프라자 1층 125호</t>
+          <t>인천광역시 연수구 센트럴로 194 a동 2층 221호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/o_haruhair</t>
+          <t>https://www.instagram.com/juno.hairsalon?igsh=cTI0NTZycDM4NWM%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5723,7 +5703,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5743,13 +5723,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>6920</v>
+        <v>18793</v>
       </c>
       <c r="Q57" t="n">
-        <v>2678</v>
+        <v>1017</v>
       </c>
       <c r="R57" t="n">
-        <v>9598</v>
+        <v>19810</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5758,17 +5738,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1708240266</t>
+          <t>1341167720</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708240266</t>
+          <t>https://m.place.naver.com/place/1341167720</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5780,29 +5760,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아치헤어 송도센트럴파크점</t>
+          <t>와스 WHAS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>archihair@naver.com</t>
+          <t>whashair@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1395-5750</t>
+          <t>0507-1378-7472</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 해돋이로171번길 11 201호</t>
+          <t>인천광역시 연수구 송도미래로11번길 27 스마트스퀘어 B동 215호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/archihair</t>
+          <t>https://blog.naver.com/whashair</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5837,13 +5817,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2199</v>
+        <v>145</v>
       </c>
       <c r="Q58" t="n">
-        <v>649</v>
+        <v>14</v>
       </c>
       <c r="R58" t="n">
-        <v>2848</v>
+        <v>159</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5852,17 +5832,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1653822327</t>
+          <t>2045505953</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1653822327</t>
+          <t>https://m.place.naver.com/place/2045505953</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5874,25 +5854,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>마끼에 타임스페이스점</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>무닛</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>themoonit@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1411-5326</t>
+          <t>0507-1301-9771</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 C동 307호, 308호</t>
+          <t>인천광역시 연수구 하모니로 158 A-217호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/maquillee_songdo</t>
+          <t>https://www.instagram.com/munit__official</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5927,13 +5911,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>6233</v>
+        <v>270</v>
       </c>
       <c r="Q59" t="n">
-        <v>818</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>7051</v>
+        <v>271</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5942,51 +5926,51 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>37058951</t>
+          <t>2088334078</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37058951</t>
+          <t>https://m.place.naver.com/place/2088334078</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>로이드밤 송도점</t>
+          <t>매드맨즈헤어</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>blablakimm@naver.com</t>
+          <t>eqvopza669@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-833-6212</t>
+          <t>0507-1316-7719</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로125번길 13 아크리아1 2층 로이드밤</t>
+          <t>인천광역시 연수구 컨벤시아대로 69 밀레니엄빌딩 204호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lloydbomb_songdo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5996,7 +5980,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6017,17 +6001,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>4078</v>
+        <v>1668</v>
       </c>
       <c r="Q60" t="n">
-        <v>308</v>
+        <v>1689</v>
       </c>
       <c r="R60" t="n">
-        <v>4386</v>
+        <v>3357</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6036,17 +6020,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>37547131</t>
+          <t>1852738585</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37547131</t>
+          <t>https://m.place.naver.com/place/1852738585</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6058,29 +6042,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>라보떼헤어살롱 송도점</t>
+          <t>에이앤느 송도 타임스페이스 본점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hai1302@naver.com</t>
+          <t>aannehair@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1309-7795</t>
+          <t>0507-1445-0710</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로125번길 7 202호</t>
+          <t>인천광역시 연수구 하모니로 158 타임스페이스 B동 303, 304호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hai1302</t>
+          <t>https://youtube.com/@aannetv</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6095,7 +6079,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6115,13 +6099,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1827</v>
+        <v>3715</v>
       </c>
       <c r="Q61" t="n">
-        <v>342</v>
+        <v>1448</v>
       </c>
       <c r="R61" t="n">
-        <v>2169</v>
+        <v>5163</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6130,17 +6114,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1899802195</t>
+          <t>1640981582</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899802195</t>
+          <t>https://m.place.naver.com/place/1640981582</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6152,25 +6136,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>유얼커트 캠퍼스타운점</t>
+          <t>박승철 헤어스투디오 캠퍼스타운역점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1444-8333</t>
+          <t>0507-1404-9592</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도과학로27번길 15 아메리칸타운아이파크 상가 139호 유얼커트</t>
+          <t>인천광역시 연수구 송도과학로27번길 27 204-C동 2층 C241호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yourcut_campus</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6180,7 +6164,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6201,17 +6185,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1710</v>
+        <v>1147</v>
       </c>
       <c r="Q62" t="n">
-        <v>23</v>
+        <v>1052</v>
       </c>
       <c r="R62" t="n">
-        <v>1733</v>
+        <v>2199</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6220,17 +6204,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1166620197</t>
+          <t>2025219384</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166620197</t>
+          <t>https://m.place.naver.com/place/2025219384</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6242,34 +6226,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>준오헤어 송도홈플러스점</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>whitemilkiss@naver.com</t>
-        </is>
-      </c>
+          <t>몰트베</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1398-0605</t>
+          <t>0507-1440-8389</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 165 홈플러스2층 준오헤어송도홈플러스점</t>
+          <t>인천광역시 연수구 인천타워대로 257 D동 2층 203호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://junohair.com/</t>
+          <t>https://www.instagram.com/moltbe.hair</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6299,13 +6279,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5370</v>
+        <v>604</v>
       </c>
       <c r="Q63" t="n">
-        <v>302</v>
+        <v>70</v>
       </c>
       <c r="R63" t="n">
-        <v>5672</v>
+        <v>674</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6314,17 +6294,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>37207297</t>
+          <t>1133641661</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37207297</t>
+          <t>https://m.place.naver.com/place/1133641661</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6336,29 +6316,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>로맨시아 송도본점</t>
+          <t>이움헤어 송도점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kshcym10@naver.com</t>
+          <t>eeem_hair@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>032-851-0606</t>
+          <t>0507-1469-4081</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 랜드마크로 68 판매시설 301동 231호 로맨시아 송도본점</t>
+          <t>인천광역시 연수구 컨벤시아대로 116 134호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/romancia__salon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6368,7 +6348,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6389,17 +6369,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3730</v>
+        <v>348</v>
       </c>
       <c r="Q64" t="n">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="R64" t="n">
-        <v>3778</v>
+        <v>472</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6408,17 +6388,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1759321108</t>
+          <t>1695585334</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759321108</t>
+          <t>https://m.place.naver.com/place/1695585334</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6410,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>고정현헤어 송도오네스타점</t>
+          <t>고정현헤어 쉐라톤점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6441,13 +6421,13 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1304-3256</t>
+          <t>0507-1411-3256</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 157 오네스타 지하 1층에 위치해 있습니다</t>
+          <t>인천광역시 연수구 컨벤시아대로 153 쉐라톤호텔 6층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6487,13 +6467,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>8498</v>
+        <v>1693</v>
       </c>
       <c r="Q65" t="n">
-        <v>1088</v>
+        <v>1003</v>
       </c>
       <c r="R65" t="n">
-        <v>9586</v>
+        <v>2696</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6502,17 +6482,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1691517290</t>
+          <t>13397872</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691517290</t>
+          <t>https://m.place.naver.com/place/13397872</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6524,29 +6504,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>아이디헤어 송도센트럴파크점</t>
+          <t>아이콘헤어살롱 송도트리플타워점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>rnalghoi@naver.com</t>
+          <t>iconkwon@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1490-1682</t>
+          <t>0507-1402-2998</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 160 판매시설 C동 2층 아이디헤어</t>
+          <t>인천광역시 연수구 송도과학로28번길 50 트리플타워west 2층 208호 아이콘헤어살롱</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rnalghoi?tab=1</t>
+          <t>https://blog.naver.com/iconkwon</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6581,13 +6561,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1382</v>
+        <v>2907</v>
       </c>
       <c r="Q66" t="n">
-        <v>1428</v>
+        <v>141</v>
       </c>
       <c r="R66" t="n">
-        <v>2810</v>
+        <v>3048</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6596,17 +6576,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2010746176</t>
+          <t>37927793</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2010746176</t>
+          <t>https://m.place.naver.com/place/37927793</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6618,29 +6598,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>소유헤어</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>dmsrud_0724@naver.com</t>
-        </is>
-      </c>
+          <t>트라움 헤어</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1433-1221</t>
+          <t>070-4035-2802</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 센트럴로 232 센트럴1차상가 E동 150호 소유헤어</t>
+          <t>인천광역시 연수구 해돋이로 160-14 제이블록 3층 306호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dmsrud_0724</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6650,12 +6626,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6675,13 +6651,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1792</v>
+        <v>57</v>
       </c>
       <c r="Q67" t="n">
-        <v>2212</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>4004</v>
+        <v>59</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6690,17 +6666,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1483623620</t>
+          <t>2070075361</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1483623620</t>
+          <t>https://m.place.naver.com/place/2070075361</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6712,29 +6688,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>토리헤어 송도신도시점</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>nl7070@naver.com</t>
-        </is>
-      </c>
+          <t>노이브헤어</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1382-3911</t>
+          <t>0507-1348-5301</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 122 송도프라자 3층</t>
+          <t>인천광역시 연수구 인천타워대로 301 2층 B동 2057호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/noive.hair_official?igsh=MTR1aXZydjk3NnF5bg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6744,7 +6716,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6765,17 +6737,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2510</v>
+        <v>571</v>
       </c>
       <c r="Q68" t="n">
-        <v>26</v>
+        <v>177</v>
       </c>
       <c r="R68" t="n">
-        <v>2536</v>
+        <v>748</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6784,17 +6756,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1189703707</t>
+          <t>2086898474</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189703707</t>
+          <t>https://m.place.naver.com/place/2086898474</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6806,29 +6778,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>라벨르봄헤어살롱 송도본점</t>
+          <t>스타일하우스 송도퍼스트파크점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kwangsu_pyo@naver.com</t>
+          <t>stylehousefp@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1305-2402</t>
+          <t>0507-1442-7926</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 365 오피스텔 201동 2층 213호</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 54 닥터플러스몰 A동 216호 스타일하우스 송도퍼스트파크점</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@stylehouse_r</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6838,7 +6810,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6859,17 +6831,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="Q69" t="n">
-        <v>922</v>
+        <v>1023</v>
       </c>
       <c r="R69" t="n">
-        <v>1670</v>
+        <v>1769</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6878,17 +6850,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1328540463</t>
+          <t>1895840787</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328540463</t>
+          <t>https://m.place.naver.com/place/1895840787</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6900,29 +6872,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>니드어스헤어 인천송도점</t>
+          <t>무울헤어스튜디오</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>needus109@naver.com</t>
+          <t>tldms105@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1487-7300</t>
+          <t>0507-1328-7105</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 신송로 157-15 제이큐브건물 2층 202호</t>
+          <t>인천광역시 연수구 컨벤시아대로230번길 42 송도아라플라자 상가 117호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/needus_official</t>
+          <t>https://blog.naver.com/tldms105</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6937,7 +6909,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6957,13 +6929,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1186</v>
+        <v>3100</v>
       </c>
       <c r="Q70" t="n">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="R70" t="n">
-        <v>1345</v>
+        <v>3335</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6972,51 +6944,51 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2004520377</t>
+          <t>1625864632</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2004520377</t>
+          <t>https://m.place.naver.com/place/1625864632</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>오프블랙바버샵</t>
+          <t>덕무드헤어 송도타임스페이스점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kyoung070700@naver.com</t>
+          <t>wooduk89@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1371-7969</t>
+          <t>0507-1449-0237</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 하모니로 158 타임스페이스 C동 지하1층 B20호</t>
+          <t>인천광역시 연수구 하모니로 158 B동 314호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kyoung070700</t>
+          <t>https://blog.naver.com/wooduk89</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7051,13 +7023,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1160</v>
+        <v>1242</v>
       </c>
       <c r="Q71" t="n">
-        <v>96</v>
+        <v>429</v>
       </c>
       <c r="R71" t="n">
-        <v>1256</v>
+        <v>1671</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,51 +7038,51 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1841393034</t>
+          <t>1163645359</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1841393034</t>
+          <t>https://m.place.naver.com/place/1163645359</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>맨즈헤어 FACE</t>
+          <t>본비반트헤어 송도센트럴파크점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>facebarbershop@naver.com</t>
+          <t>pleas12@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1370-9578</t>
+          <t>0507-1445-2352</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 컨벤시아대로 126 2층 205호</t>
+          <t>인천광역시 연수구 센트럴로 232 D동 202호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/facebarbershop</t>
+          <t>https://blog.naver.com/pleas12</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7145,13 +7117,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>327</v>
+        <v>2673</v>
       </c>
       <c r="Q72" t="n">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="R72" t="n">
-        <v>356</v>
+        <v>2843</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,47 +7132,51 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1863796057</t>
+          <t>35372752</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1863796057</t>
+          <t>https://m.place.naver.com/place/35372752</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>젠틀루 뉴욕 오네스타점</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>포레브헤어</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>loveru90@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1300-0321</t>
+          <t>0507-1487-8813</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 송도국제대로 157 오네스타 지하 1층 A-B06호</t>
+          <t>인천광역시 연수구 하모니로178번길 6 3층 312호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://gentleloup.com/</t>
+          <t>https://www.instagram.com/foreve_official</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7235,13 +7211,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1327</v>
+        <v>2074</v>
       </c>
       <c r="Q73" t="n">
-        <v>65</v>
+        <v>648</v>
       </c>
       <c r="R73" t="n">
-        <v>1392</v>
+        <v>2722</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7250,17 +7226,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1529521111</t>
+          <t>1653032976</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529521111</t>
+          <t>https://m.place.naver.com/place/1653032976</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7272,29 +7248,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>원트맨즈헤어 송도본점</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>bngu28@naver.com</t>
-        </is>
-      </c>
+          <t>젠틀루 뉴욕 오네스타점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1432-2428</t>
+          <t>0507-1300-0321</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로197번길 16 2층 210호 원트맨즈헤어</t>
+          <t>인천광역시 연수구 송도국제대로 157 오네스타 지하 1층 A-B06호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bngu28</t>
+          <t>http://gentleloup.com/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7309,7 +7281,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7325,17 +7297,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>640</v>
+        <v>1341</v>
       </c>
       <c r="Q74" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="R74" t="n">
-        <v>701</v>
+        <v>1406</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7344,17 +7316,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1392215030</t>
+          <t>1529521111</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1392215030</t>
+          <t>https://m.place.naver.com/place/1529521111</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7366,29 +7338,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>엔투라지바버샵 송도점</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>n2rage_songdo@naver.com</t>
-        </is>
-      </c>
+          <t>로드 바버샵 송도</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1400-2262</t>
+          <t>0507-1351-0427</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 아트센터대로 203 센트럴파크푸르지오시티 B동 133호</t>
+          <t>인천광역시 연수구 컨벤시아대로 100 송도힐스테이트 602동 145호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/n2ragebarbershop</t>
+          <t>https://www.instagram.com/rodbarbershop_</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7423,13 +7391,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>654</v>
+        <v>790</v>
       </c>
       <c r="Q75" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="R75" t="n">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7438,17 +7406,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1335997088</t>
+          <t>1710795723</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1335997088</t>
+          <t>https://m.place.naver.com/place/1710795723</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7460,29 +7428,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>더 페이드 바버샵</t>
+          <t>맨즈헤어 FACE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>awb88@naver.com</t>
+          <t>facebarbershop@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1350-7855</t>
+          <t>0507-1370-9578</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 연수구 인천타워대로 301 A동 상가 2층 2032호 더 페이드 바버샵</t>
+          <t>인천광역시 연수구 컨벤시아대로 126 2층 205호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/awb88</t>
+          <t>https://blog.naver.com/facebarbershop</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7513,17 +7481,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>152</v>
+        <v>345</v>
       </c>
       <c r="Q76" t="n">
         <v>29</v>
       </c>
       <c r="R76" t="n">
-        <v>181</v>
+        <v>374</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7532,17 +7500,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2055852219</t>
+          <t>1863796057</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055852219</t>
+          <t>https://m.place.naver.com/place/1863796057</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
